--- a/PFP-C/Input data and Generated Schedule/66.xlsx
+++ b/PFP-C/Input data and Generated Schedule/66.xlsx
@@ -30775,7 +30775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30800,7 +30800,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>objective all vehicle travel individually</t>
+          <t>objective_all_vehicle_travel_individually</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -30810,7 +30810,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>objective LLA</t>
+          <t>objective_LLA</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -30820,11 +30820,131 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>objective lb</t>
+          <t>objective_lb</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>38.16150000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_5</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_10</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_10</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_15</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_15</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_20</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_20</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_25</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_25</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_30</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_30</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -42138,7 +42258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42174,25 +42294,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>before_due_time_(minute)</t>
+          <t>duration_trip_alone_(minute)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>duration_trip_alone_(minute)</t>
+          <t>Saving_time_(minute)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Saving_time_(minute)</t>
+          <t>Saving_time(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Saving_time(%)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Exit</t>
         </is>
@@ -42225,18 +42340,15 @@
         <v>7.658959537572244</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>291.3318318318318</v>
       </c>
       <c r="I2" t="n">
-        <v>291.3318318318318</v>
+        <v>3.978978978978974</v>
       </c>
       <c r="J2" t="n">
-        <v>3.978978978978974</v>
-      </c>
-      <c r="K2" t="n">
         <v>1.365789297365829</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -42269,18 +42381,15 @@
         <v>7.832898172323742</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>325.5382882882883</v>
       </c>
       <c r="I3" t="n">
-        <v>325.5382882882883</v>
+        <v>4.504504504504495</v>
       </c>
       <c r="J3" t="n">
-        <v>4.504504504504495</v>
-      </c>
-      <c r="K3" t="n">
         <v>1.383709587031871</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -42313,18 +42422,15 @@
         <v>6.293532338308448</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>356.1546546546547</v>
       </c>
       <c r="I4" t="n">
-        <v>356.1546546546547</v>
+        <v>3.798798798798793</v>
       </c>
       <c r="J4" t="n">
-        <v>3.798798798798793</v>
-      </c>
-      <c r="K4" t="n">
         <v>1.066614952002326</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -42357,18 +42463,15 @@
         <v>7.885117493472574</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>339.6524024024024</v>
       </c>
       <c r="I5" t="n">
-        <v>339.6524024024024</v>
+        <v>4.534534534534528</v>
       </c>
       <c r="J5" t="n">
-        <v>4.534534534534528</v>
-      </c>
-      <c r="K5" t="n">
         <v>1.335051512211078</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -42401,18 +42504,15 @@
         <v>3.757225433526008</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5248605367029313</v>
+        <v>288.0285285285285</v>
       </c>
       <c r="I6" t="n">
-        <v>288.0285285285285</v>
+        <v>1.95195195195195</v>
       </c>
       <c r="J6" t="n">
-        <v>1.95195195195195</v>
-      </c>
-      <c r="K6" t="n">
         <v>0.6776939638319939</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -42445,18 +42545,15 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>-10.63057605418561</v>
+        <v>291.3370870870871</v>
       </c>
       <c r="I7" t="n">
-        <v>291.3370870870871</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -42489,18 +42586,15 @@
         <v>5.509259259259268</v>
       </c>
       <c r="H8" t="n">
-        <v>-23.34817354186191</v>
+        <v>191.4294294294294</v>
       </c>
       <c r="I8" t="n">
-        <v>191.4294294294294</v>
+        <v>1.78678678678679</v>
       </c>
       <c r="J8" t="n">
-        <v>1.78678678678679</v>
-      </c>
-      <c r="K8" t="n">
         <v>0.933391899099553</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -42533,18 +42627,15 @@
         <v>5.506329113924048</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>297.3603603603605</v>
       </c>
       <c r="I9" t="n">
-        <v>297.3603603603605</v>
+        <v>2.612612612612611</v>
       </c>
       <c r="J9" t="n">
-        <v>2.612612612612611</v>
-      </c>
-      <c r="K9" t="n">
         <v>0.8786015087708661</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -42577,18 +42668,15 @@
         <v>4.493670886075947</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>276.039039039039</v>
       </c>
       <c r="I10" t="n">
-        <v>276.039039039039</v>
+        <v>2.13213213213213</v>
       </c>
       <c r="J10" t="n">
-        <v>2.13213213213213</v>
-      </c>
-      <c r="K10" t="n">
         <v>0.7724023890079519</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -42621,18 +42709,15 @@
         <v>0.9660574412532615</v>
       </c>
       <c r="H11" t="n">
-        <v>-24.18978143744908</v>
+        <v>322.5352852852853</v>
       </c>
       <c r="I11" t="n">
-        <v>322.5352852852853</v>
+        <v>0.5555555555555544</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5555555555555544</v>
-      </c>
-      <c r="K11" t="n">
         <v>0.1722464427618084</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -42665,18 +42750,15 @@
         <v>8.437499999999989</v>
       </c>
       <c r="H12" t="n">
-        <v>-16.57906703388346</v>
+        <v>228.6366366366366</v>
       </c>
       <c r="I12" t="n">
-        <v>228.6366366366366</v>
+        <v>3.243243243243239</v>
       </c>
       <c r="J12" t="n">
-        <v>3.243243243243239</v>
-      </c>
-      <c r="K12" t="n">
         <v>1.418514237679939</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -42709,18 +42791,15 @@
         <v>2.487562189054728</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>354.0525525525525</v>
       </c>
       <c r="I13" t="n">
-        <v>354.0525525525525</v>
+        <v>1.501501501501503</v>
       </c>
       <c r="J13" t="n">
-        <v>1.501501501501503</v>
-      </c>
-      <c r="K13" t="n">
         <v>0.4240900088634815</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -42753,18 +42832,15 @@
         <v>9.033942558746725</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>318.6313813813814</v>
       </c>
       <c r="I14" t="n">
-        <v>318.6313813813814</v>
+        <v>5.195195195195189</v>
       </c>
       <c r="J14" t="n">
-        <v>5.195195195195189</v>
-      </c>
-      <c r="K14" t="n">
         <v>1.630471917948619</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -42797,18 +42873,15 @@
         <v>6.704035874439469</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>389.454954954955</v>
       </c>
       <c r="I15" t="n">
-        <v>389.454954954955</v>
+        <v>4.489489489489495</v>
       </c>
       <c r="J15" t="n">
-        <v>4.489489489489495</v>
-      </c>
-      <c r="K15" t="n">
         <v>1.152762195568614</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -42841,18 +42914,15 @@
         <v>8.587443946188339</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>380.1456456456457</v>
       </c>
       <c r="I16" t="n">
-        <v>380.1456456456457</v>
+        <v>5.75075075075075</v>
       </c>
       <c r="J16" t="n">
-        <v>5.75075075075075</v>
-      </c>
-      <c r="K16" t="n">
         <v>1.512775647076946</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -42885,18 +42955,15 @@
         <v>3.833992094861659</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>216.3265765765766</v>
       </c>
       <c r="I17" t="n">
-        <v>216.3265765765766</v>
+        <v>1.456456456456456</v>
       </c>
       <c r="J17" t="n">
-        <v>1.456456456456456</v>
-      </c>
-      <c r="K17" t="n">
         <v>0.6732674641762708</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -42929,18 +42996,15 @@
         <v>7.075098814229241</v>
       </c>
       <c r="H18" t="n">
-        <v>-16.54222673554079</v>
+        <v>225.9361861861862</v>
       </c>
       <c r="I18" t="n">
-        <v>225.9361861861862</v>
+        <v>2.687687687687685</v>
       </c>
       <c r="J18" t="n">
-        <v>2.687687687687685</v>
-      </c>
-      <c r="K18" t="n">
         <v>1.189578231382933</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -42973,18 +43037,15 @@
         <v>10</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.813880456219067</v>
+        <v>220.2304804804805</v>
       </c>
       <c r="I19" t="n">
-        <v>220.2304804804805</v>
+        <v>3.7987987987988</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7987987987988</v>
-      </c>
-      <c r="K19" t="n">
         <v>1.724919634426124</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -43017,18 +43078,15 @@
         <v>8.53754940711463</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>217.5277777777778</v>
       </c>
       <c r="I20" t="n">
-        <v>217.5277777777778</v>
+        <v>3.243243243243246</v>
       </c>
       <c r="J20" t="n">
-        <v>3.243243243243246</v>
-      </c>
-      <c r="K20" t="n">
         <v>1.490955902908401</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -43061,18 +43119,15 @@
         <v>8.93063583815028</v>
       </c>
       <c r="H21" t="n">
-        <v>-26.16839169867546</v>
+        <v>298.539039039039</v>
       </c>
       <c r="I21" t="n">
-        <v>298.539039039039</v>
+        <v>4.639639639639635</v>
       </c>
       <c r="J21" t="n">
-        <v>4.639639639639635</v>
-      </c>
-      <c r="K21" t="n">
         <v>1.554114883793447</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -43105,18 +43160,15 @@
         <v>4.072847682119198</v>
       </c>
       <c r="H22" t="n">
-        <v>-10.72075999278394</v>
+        <v>258.0315315315315</v>
       </c>
       <c r="I22" t="n">
-        <v>258.0315315315315</v>
+        <v>1.846846846846843</v>
       </c>
       <c r="J22" t="n">
-        <v>1.846846846846843</v>
-      </c>
-      <c r="K22" t="n">
         <v>0.7157446362795231</v>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -43149,18 +43201,15 @@
         <v>1.123595505617978</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>309.0420420420421</v>
       </c>
       <c r="I23" t="n">
-        <v>309.0420420420421</v>
+        <v>0.6006006006006011</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6006006006006011</v>
-      </c>
-      <c r="K23" t="n">
         <v>0.1943426844555005</v>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -43193,18 +43242,15 @@
         <v>2.890624999999994</v>
       </c>
       <c r="H24" t="n">
-        <v>-19.84484213573728</v>
+        <v>226.2342342342343</v>
       </c>
       <c r="I24" t="n">
-        <v>226.2342342342343</v>
+        <v>1.111111111111109</v>
       </c>
       <c r="J24" t="n">
-        <v>1.111111111111109</v>
-      </c>
-      <c r="K24" t="n">
         <v>0.4911330572369106</v>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -43237,18 +43283,15 @@
         <v>2.08333333333333</v>
       </c>
       <c r="H25" t="n">
-        <v>-23.11816225788255</v>
+        <v>171.009009009009</v>
       </c>
       <c r="I25" t="n">
-        <v>171.009009009009</v>
+        <v>0.6756756756756745</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6756756756756745</v>
-      </c>
-      <c r="K25" t="n">
         <v>0.3951111579390996</v>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -43281,18 +43324,15 @@
         <v>6.758893280632421</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>245.1554054054054</v>
       </c>
       <c r="I26" t="n">
-        <v>245.1554054054054</v>
+        <v>2.567567567567571</v>
       </c>
       <c r="J26" t="n">
-        <v>2.567567567567571</v>
-      </c>
-      <c r="K26" t="n">
         <v>1.047322437505169</v>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -43309,7 +43349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43335,20 +43375,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>before_due_time_(minute)</t>
+          <t>duration_trip_alone_(minute)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>duration_trip_alone_(minute)</t>
+          <t>Saving_time_(minute)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Saving_time_(minute)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Saving_time(%)</t>
         </is>
@@ -43381,9 +43416,6 @@
       <c r="H2" t="n">
         <v>25</v>
       </c>
-      <c r="I2" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -43404,15 +43436,12 @@
         <v>5.618404208008141</v>
       </c>
       <c r="F3" t="n">
-        <v>-7.019228875236884</v>
+        <v>281.5344144144144</v>
       </c>
       <c r="G3" t="n">
-        <v>281.5344144144144</v>
+        <v>2.746546546546545</v>
       </c>
       <c r="H3" t="n">
-        <v>2.746546546546545</v>
-      </c>
-      <c r="I3" t="n">
         <v>0.9680242259729702</v>
       </c>
     </row>
@@ -43435,15 +43464,12 @@
         <v>2.885756050621178</v>
       </c>
       <c r="F4" t="n">
-        <v>9.795558149819664</v>
+        <v>59.6501052666797</v>
       </c>
       <c r="G4" t="n">
-        <v>59.6501052666797</v>
+        <v>1.608265821120318</v>
       </c>
       <c r="H4" t="n">
-        <v>1.608265821120318</v>
-      </c>
-      <c r="I4" t="n">
         <v>0.4998350992006501</v>
       </c>
     </row>
@@ -43466,15 +43492,12 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-26.16839169867546</v>
+        <v>171.009009009009</v>
       </c>
       <c r="G5" t="n">
-        <v>171.009009009009</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -43497,15 +43520,12 @@
         <v>3.757225433526008</v>
       </c>
       <c r="F6" t="n">
-        <v>-16.54222673554079</v>
+        <v>226.2342342342343</v>
       </c>
       <c r="G6" t="n">
-        <v>226.2342342342343</v>
+        <v>1.501501501501503</v>
       </c>
       <c r="H6" t="n">
-        <v>1.501501501501503</v>
-      </c>
-      <c r="I6" t="n">
         <v>0.6732674641762708</v>
       </c>
     </row>
@@ -43528,15 +43548,12 @@
         <v>6.293532338308448</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>291.3318318318318</v>
       </c>
       <c r="G7" t="n">
-        <v>291.3318318318318</v>
+        <v>2.612612612612611</v>
       </c>
       <c r="H7" t="n">
-        <v>2.612612612612611</v>
-      </c>
-      <c r="I7" t="n">
         <v>1.047322437505169</v>
       </c>
     </row>
@@ -43559,15 +43576,12 @@
         <v>7.885117493472574</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>322.5352852852853</v>
       </c>
       <c r="G8" t="n">
-        <v>322.5352852852853</v>
+        <v>3.978978978978974</v>
       </c>
       <c r="H8" t="n">
-        <v>3.978978978978974</v>
-      </c>
-      <c r="I8" t="n">
         <v>1.383709587031871</v>
       </c>
     </row>
@@ -43590,15 +43604,12 @@
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>389.454954954955</v>
       </c>
       <c r="G9" t="n">
-        <v>389.454954954955</v>
+        <v>5.75075075075075</v>
       </c>
       <c r="H9" t="n">
-        <v>5.75075075075075</v>
-      </c>
-      <c r="I9" t="n">
         <v>1.724919634426124</v>
       </c>
     </row>
